--- a/Day 1/Guerrilla AI - Day 1 - Demo Start.xlsx
+++ b/Day 1/Guerrilla AI - Day 1 - Demo Start.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30520"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\guerilla-ai-for-excel\Day 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E03AB71D-7D81-4677-BDEB-21EB1637362D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C245BB-FCD6-4DF4-804C-B61A26EEDDF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,25 @@
     <sheet name="steps" sheetId="1" r:id="rId1"/>
     <sheet name="raw-export" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="147">
   <si>
     <t>Day 1: The AI already hiding in your Excel</t>
   </si>
@@ -108,12 +121,6 @@
     <t xml:space="preserve">Northeast </t>
   </si>
   <si>
-    <t xml:space="preserve">4 </t>
-  </si>
-  <si>
-    <t>$42.00</t>
-  </si>
-  <si>
     <t>SO-10402</t>
   </si>
   <si>
@@ -129,9 +136,6 @@
     <t>Northeast</t>
   </si>
   <si>
-    <t>$379.00</t>
-  </si>
-  <si>
     <t>SO-10403</t>
   </si>
   <si>
@@ -159,9 +163,6 @@
     <t>2/17/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">$379.00 </t>
-  </si>
-  <si>
     <t>SO-10410</t>
   </si>
   <si>
@@ -174,9 +175,6 @@
     <t xml:space="preserve">midwest </t>
   </si>
   <si>
-    <t xml:space="preserve">$219.00 </t>
-  </si>
-  <si>
     <t>SO-10412</t>
   </si>
   <si>
@@ -186,9 +184,6 @@
     <t>northeast</t>
   </si>
   <si>
-    <t>$219.00</t>
-  </si>
-  <si>
     <t>SO-10413</t>
   </si>
   <si>
@@ -207,9 +202,6 @@
     <t>Toner Cartridge - Office Supplies</t>
   </si>
   <si>
-    <t>$89.00</t>
-  </si>
-  <si>
     <t>SO-10415</t>
   </si>
   <si>
@@ -225,18 +217,12 @@
     <t xml:space="preserve">West </t>
   </si>
   <si>
-    <t>$549.00</t>
-  </si>
-  <si>
     <t>SO-10417</t>
   </si>
   <si>
     <t>3/27/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">$549.00 </t>
-  </si>
-  <si>
     <t>SO-10418</t>
   </si>
   <si>
@@ -276,9 +262,6 @@
     <t>2/22/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">$42.00 </t>
-  </si>
-  <si>
     <t>SO-10424</t>
   </si>
   <si>
@@ -297,9 +280,6 @@
     <t>Conference Phone - Technology</t>
   </si>
   <si>
-    <t>$269.00</t>
-  </si>
-  <si>
     <t>SO-10429</t>
   </si>
   <si>
@@ -348,9 +328,6 @@
     <t>SO-10443</t>
   </si>
   <si>
-    <t xml:space="preserve">15 </t>
-  </si>
-  <si>
     <t>SO-10444</t>
   </si>
   <si>
@@ -462,9 +439,6 @@
     <t>2026-04-12</t>
   </si>
   <si>
-    <t xml:space="preserve">$269.00 </t>
-  </si>
-  <si>
     <t>SO-10440</t>
   </si>
   <si>
@@ -496,9 +470,6 @@
   </si>
   <si>
     <t>2026-05-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$89.00 </t>
   </si>
   <si>
     <t>SO-10452</t>
@@ -520,6 +491,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+  </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -632,7 +607,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -642,6 +617,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -661,6 +640,9 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -981,28 +963,28 @@
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6"/>
+      <c r="C2" s="10"/>
     </row>
     <row r="3" spans="2:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="6"/>
+      <c r="C3" s="10"/>
     </row>
     <row r="5" spans="2:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="6"/>
+      <c r="C5" s="10"/>
     </row>
     <row r="6" spans="2:3" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="10"/>
     </row>
     <row r="7" spans="2:3" ht="102" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="2" t="s">
@@ -1014,16 +996,16 @@
     </row>
     <row r="8" spans="2:3" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="10" spans="2:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="10"/>
     </row>
     <row r="11" spans="2:3" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6"/>
+      <c r="C11" s="10"/>
     </row>
     <row r="12" spans="2:3" ht="102" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
@@ -1035,16 +1017,16 @@
     </row>
     <row r="13" spans="2:3" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="14" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="10"/>
     </row>
     <row r="15" spans="2:3" ht="23" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6"/>
+      <c r="C15" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1063,19 +1045,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="3" max="3" width="30.265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12" style="8" customWidth="1"/>
+    <col min="7" max="7" width="16" style="6" customWidth="1"/>
+    <col min="8" max="8" width="12" style="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>12</v>
       </c>
@@ -1091,17 +1074,17 @@
       <c r="E1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="17" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -1117,334 +1100,335 @@
       <c r="E2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="8">
+        <v>4</v>
+      </c>
+      <c r="G2" s="6">
+        <v>42</v>
+      </c>
+      <c r="H2" s="18">
+        <v>168</v>
+      </c>
+      <c r="K2" s="5"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
         <v>25</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B3" t="s">
         <v>26</v>
       </c>
-      <c r="H2">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>28</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>29</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" s="8">
+        <v>23</v>
+      </c>
+      <c r="G3" s="6">
+        <v>379</v>
+      </c>
+      <c r="H3" s="18">
+        <v>8717</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B4" t="s">
         <v>31</v>
       </c>
-      <c r="F3">
-        <v>23</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="C4" t="s">
         <v>32</v>
       </c>
-      <c r="H3">
-        <v>8717</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
+      <c r="F4" s="8">
+        <v>19</v>
+      </c>
+      <c r="G4" s="6">
+        <v>379</v>
+      </c>
+      <c r="H4" s="18">
+        <v>7201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
         <v>34</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
         <v>35</v>
       </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="C5" t="s">
         <v>36</v>
-      </c>
-      <c r="F4">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4">
-        <v>7201</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" t="s">
-        <v>39</v>
       </c>
       <c r="D5" t="s">
         <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5">
+        <v>29</v>
+      </c>
+      <c r="F5" s="8">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5">
+      <c r="G5" s="6">
+        <v>42</v>
+      </c>
+      <c r="H5" s="18">
         <v>168</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6">
+        <v>29</v>
+      </c>
+      <c r="F6" s="8">
         <v>4</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="6">
+        <v>379</v>
+      </c>
+      <c r="H6" s="18">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>42</v>
       </c>
-      <c r="H6">
-        <v>1516</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="F7" s="8">
+        <v>22</v>
+      </c>
+      <c r="G7" s="6">
+        <v>219</v>
+      </c>
+      <c r="H7" s="18">
+        <v>4818</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
         <v>43</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>44</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7">
-        <v>22</v>
-      </c>
-      <c r="G7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7">
-        <v>4818</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" t="s">
-        <v>49</v>
       </c>
       <c r="C8" t="s">
         <v>22</v>
       </c>
       <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
         <v>45</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" s="8">
+        <v>16</v>
+      </c>
+      <c r="G8" s="6">
+        <v>219</v>
+      </c>
+      <c r="H8" s="18">
+        <v>3504</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="8">
+        <v>22</v>
+      </c>
+      <c r="G9" s="6">
+        <v>379</v>
+      </c>
+      <c r="H9" s="18">
+        <v>8338</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
         <v>50</v>
       </c>
-      <c r="F8">
-        <v>16</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
         <v>51</v>
       </c>
-      <c r="H8">
-        <v>3504</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="8">
+        <v>17</v>
+      </c>
+      <c r="G10" s="6">
+        <v>89</v>
+      </c>
+      <c r="H10" s="18">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
         <v>52</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B11" t="s">
         <v>53</v>
       </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="8">
+        <v>14</v>
+      </c>
+      <c r="G11" s="6">
+        <v>89</v>
+      </c>
+      <c r="H11" s="18">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
         <v>54</v>
       </c>
-      <c r="F9">
-        <v>22</v>
-      </c>
-      <c r="G9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9">
-        <v>8338</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
         <v>55</v>
       </c>
-      <c r="B10" t="s">
+      <c r="E12" t="s">
         <v>56</v>
       </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="F12" s="8">
+        <v>19</v>
+      </c>
+      <c r="G12" s="6">
+        <v>549</v>
+      </c>
+      <c r="H12" s="18">
+        <v>10431</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
         <v>57</v>
       </c>
-      <c r="E10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10">
-        <v>17</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="B13" t="s">
         <v>58</v>
-      </c>
-      <c r="H10">
-        <v>1513</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
-        <v>58</v>
-      </c>
-      <c r="H11">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12">
-        <v>19</v>
-      </c>
-      <c r="G12" t="s">
-        <v>64</v>
-      </c>
-      <c r="H12">
-        <v>10431</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" t="s">
-        <v>66</v>
       </c>
       <c r="C13" t="s">
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13">
+        <v>29</v>
+      </c>
+      <c r="F13" s="8">
         <v>20</v>
       </c>
-      <c r="G13" t="s">
-        <v>67</v>
-      </c>
-      <c r="H13">
+      <c r="G13" s="6">
+        <v>549</v>
+      </c>
+      <c r="H13" s="18">
         <v>10980</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
         <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14">
+        <v>42</v>
+      </c>
+      <c r="F14" s="8">
         <v>17</v>
       </c>
-      <c r="G14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14">
+      <c r="G14" s="6">
+        <v>42</v>
+      </c>
+      <c r="H14" s="18">
         <v>714</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
         <v>22</v>
@@ -1453,1071 +1437,1077 @@
         <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15">
+        <v>48</v>
+      </c>
+      <c r="F15" s="8">
         <v>4</v>
       </c>
-      <c r="G15" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15">
+      <c r="G15" s="6">
+        <v>42</v>
+      </c>
+      <c r="H15" s="18">
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
         <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16">
+        <v>42</v>
+      </c>
+      <c r="F16" s="8">
         <v>9</v>
       </c>
-      <c r="G16" t="s">
-        <v>47</v>
-      </c>
-      <c r="H16">
+      <c r="G16" s="6">
+        <v>219</v>
+      </c>
+      <c r="H16" s="18">
         <v>1971</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E17" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17">
+        <v>67</v>
+      </c>
+      <c r="F17" s="8">
         <v>8</v>
       </c>
-      <c r="G17" t="s">
-        <v>51</v>
-      </c>
-      <c r="H17">
+      <c r="G17" s="6">
+        <v>219</v>
+      </c>
+      <c r="H17" s="18">
         <v>1752</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E18" t="s">
         <v>24</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="8">
         <v>22</v>
       </c>
-      <c r="G18" t="s">
-        <v>51</v>
-      </c>
-      <c r="H18">
+      <c r="G18" s="6">
+        <v>219</v>
+      </c>
+      <c r="H18" s="18">
         <v>4818</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
         <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
-      </c>
-      <c r="F19">
+        <v>56</v>
+      </c>
+      <c r="F19" s="8">
         <v>20</v>
       </c>
-      <c r="G19" t="s">
-        <v>81</v>
-      </c>
-      <c r="H19">
+      <c r="G19" s="6">
+        <v>42</v>
+      </c>
+      <c r="H19" s="18">
         <v>840</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20">
+        <v>74</v>
+      </c>
+      <c r="F20" s="8">
         <v>13</v>
       </c>
-      <c r="G20" t="s">
-        <v>32</v>
-      </c>
-      <c r="H20">
+      <c r="G20" s="6">
+        <v>379</v>
+      </c>
+      <c r="H20" s="18">
         <v>4927</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
         <v>22</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s">
-        <v>84</v>
-      </c>
-      <c r="F21">
+        <v>74</v>
+      </c>
+      <c r="F21" s="8">
         <v>23</v>
       </c>
-      <c r="G21" t="s">
-        <v>88</v>
-      </c>
-      <c r="H21">
+      <c r="G21" s="6">
+        <v>269</v>
+      </c>
+      <c r="H21" s="18">
         <v>6187</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
-      </c>
-      <c r="F22">
+        <v>48</v>
+      </c>
+      <c r="F22" s="8">
         <v>22</v>
       </c>
-      <c r="G22" t="s">
-        <v>64</v>
-      </c>
-      <c r="H22">
+      <c r="G22" s="6">
+        <v>549</v>
+      </c>
+      <c r="H22" s="18">
         <v>12078</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E23" t="s">
         <v>24</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="8">
         <v>10</v>
       </c>
-      <c r="G23" t="s">
-        <v>64</v>
-      </c>
-      <c r="H23">
+      <c r="G23" s="6">
+        <v>549</v>
+      </c>
+      <c r="H23" s="18">
         <v>5490</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>54</v>
-      </c>
-      <c r="F24">
+        <v>48</v>
+      </c>
+      <c r="F24" s="8">
         <v>4</v>
       </c>
-      <c r="G24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H24">
+      <c r="G24" s="6">
+        <v>219</v>
+      </c>
+      <c r="H24" s="18">
         <v>876</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E25" t="s">
-        <v>84</v>
-      </c>
-      <c r="F25">
+        <v>74</v>
+      </c>
+      <c r="F25" s="8">
         <v>13</v>
       </c>
-      <c r="G25" t="s">
-        <v>64</v>
-      </c>
-      <c r="H25">
+      <c r="G25" s="6">
+        <v>549</v>
+      </c>
+      <c r="H25" s="18">
         <v>7137</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" t="s">
         <v>41</v>
       </c>
-      <c r="C26" t="s">
+      <c r="E26" t="s">
         <v>29</v>
       </c>
-      <c r="D26" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26">
+      <c r="F26" s="8">
         <v>16</v>
       </c>
-      <c r="G26" t="s">
-        <v>51</v>
-      </c>
-      <c r="H26">
+      <c r="G26" s="6">
+        <v>219</v>
+      </c>
+      <c r="H26" s="18">
         <v>3504</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
         <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E27" t="s">
-        <v>46</v>
-      </c>
-      <c r="F27">
+        <v>42</v>
+      </c>
+      <c r="F27" s="8">
         <v>8</v>
       </c>
-      <c r="G27" t="s">
-        <v>58</v>
-      </c>
-      <c r="H27">
+      <c r="G27" s="6">
+        <v>89</v>
+      </c>
+      <c r="H27" s="18">
         <v>712</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E28" t="s">
-        <v>103</v>
-      </c>
-      <c r="F28">
+        <v>92</v>
+      </c>
+      <c r="F28" s="8">
         <v>18</v>
       </c>
-      <c r="G28" t="s">
-        <v>64</v>
-      </c>
-      <c r="H28">
+      <c r="G28" s="6">
+        <v>549</v>
+      </c>
+      <c r="H28" s="18">
         <v>9882</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s">
         <v>23</v>
       </c>
       <c r="E29" t="s">
-        <v>50</v>
-      </c>
-      <c r="F29" t="s">
-        <v>105</v>
-      </c>
-      <c r="G29" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29">
+        <v>45</v>
+      </c>
+      <c r="F29" s="8">
+        <v>15</v>
+      </c>
+      <c r="G29" s="6">
+        <v>42</v>
+      </c>
+      <c r="H29" s="18">
         <v>630</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B30" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E30" t="s">
-        <v>103</v>
-      </c>
-      <c r="F30">
+        <v>92</v>
+      </c>
+      <c r="F30" s="8">
         <v>5</v>
       </c>
-      <c r="G30" t="s">
-        <v>32</v>
-      </c>
-      <c r="H30">
+      <c r="G30" s="6">
+        <v>379</v>
+      </c>
+      <c r="H30" s="18">
         <v>1895</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="B31" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E31" t="s">
-        <v>110</v>
-      </c>
-      <c r="F31">
+        <v>98</v>
+      </c>
+      <c r="F31" s="8">
         <v>14</v>
       </c>
-      <c r="G31" t="s">
-        <v>88</v>
-      </c>
-      <c r="H31">
+      <c r="G31" s="6">
+        <v>269</v>
+      </c>
+      <c r="H31" s="18">
         <v>3766</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D32" t="s">
         <v>23</v>
       </c>
       <c r="E32" t="s">
-        <v>76</v>
-      </c>
-      <c r="F32">
+        <v>67</v>
+      </c>
+      <c r="F32" s="8">
         <v>8</v>
       </c>
-      <c r="G32" t="s">
-        <v>26</v>
-      </c>
-      <c r="H32">
+      <c r="G32" s="6">
+        <v>42</v>
+      </c>
+      <c r="H32" s="18">
         <v>336</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B33" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C33" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D33" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E33" t="s">
-        <v>115</v>
-      </c>
-      <c r="F33">
+        <v>103</v>
+      </c>
+      <c r="F33" s="8">
         <v>18</v>
       </c>
-      <c r="G33" t="s">
-        <v>58</v>
-      </c>
-      <c r="H33">
+      <c r="G33" s="6">
+        <v>89</v>
+      </c>
+      <c r="H33" s="18">
         <v>1602</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E34" t="s">
-        <v>115</v>
-      </c>
-      <c r="F34">
+        <v>103</v>
+      </c>
+      <c r="F34" s="8">
         <v>15</v>
       </c>
-      <c r="G34" t="s">
-        <v>32</v>
-      </c>
-      <c r="H34">
+      <c r="G34" s="6">
+        <v>379</v>
+      </c>
+      <c r="H34" s="18">
         <v>5685</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B35" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s">
         <v>23</v>
       </c>
       <c r="E35" t="s">
-        <v>31</v>
-      </c>
-      <c r="F35">
+        <v>29</v>
+      </c>
+      <c r="F35" s="8">
         <v>16</v>
       </c>
-      <c r="G35" t="s">
-        <v>26</v>
-      </c>
-      <c r="H35">
+      <c r="G35" s="6">
+        <v>42</v>
+      </c>
+      <c r="H35" s="18">
         <v>672</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>119</v>
-      </c>
-      <c r="H36">
+        <v>107</v>
+      </c>
+      <c r="F36" s="8">
+        <v>0</v>
+      </c>
+      <c r="G36" s="6">
+        <v>0</v>
+      </c>
+      <c r="H36" s="18">
         <v>134242</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B38" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D38" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E38" t="s">
-        <v>63</v>
-      </c>
-      <c r="F38">
+        <v>56</v>
+      </c>
+      <c r="F38" s="8">
         <v>22</v>
       </c>
-      <c r="G38" t="s">
-        <v>64</v>
-      </c>
-      <c r="H38">
+      <c r="G38" s="6">
+        <v>549</v>
+      </c>
+      <c r="H38" s="18">
         <v>12078</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D39" t="s">
         <v>23</v>
       </c>
       <c r="E39" t="s">
-        <v>84</v>
-      </c>
-      <c r="F39">
+        <v>74</v>
+      </c>
+      <c r="F39" s="8">
         <v>18</v>
       </c>
-      <c r="G39" t="s">
-        <v>26</v>
-      </c>
-      <c r="H39">
+      <c r="G39" s="6">
+        <v>42</v>
+      </c>
+      <c r="H39" s="18">
         <v>756</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C40" t="s">
         <v>22</v>
       </c>
       <c r="D40" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E40" t="s">
         <v>24</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="8">
         <v>20</v>
       </c>
-      <c r="G40" t="s">
-        <v>32</v>
-      </c>
-      <c r="H40">
+      <c r="G40" s="6">
+        <v>379</v>
+      </c>
+      <c r="H40" s="18">
         <v>7580</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B41" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C41" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D41" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E41" t="s">
-        <v>31</v>
-      </c>
-      <c r="F41">
+        <v>29</v>
+      </c>
+      <c r="F41" s="8">
         <v>5</v>
       </c>
-      <c r="G41" t="s">
-        <v>51</v>
-      </c>
-      <c r="H41">
+      <c r="G41" s="6">
+        <v>219</v>
+      </c>
+      <c r="H41" s="18">
         <v>1095</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B42" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C42" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D42" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E42" t="s">
-        <v>84</v>
-      </c>
-      <c r="F42">
+        <v>74</v>
+      </c>
+      <c r="F42" s="8">
         <v>9</v>
       </c>
-      <c r="G42" t="s">
-        <v>88</v>
-      </c>
-      <c r="H42">
+      <c r="G42" s="6">
+        <v>269</v>
+      </c>
+      <c r="H42" s="18">
         <v>2421</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B43" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C43" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E43" t="s">
-        <v>50</v>
-      </c>
-      <c r="F43">
+        <v>45</v>
+      </c>
+      <c r="F43" s="8">
         <v>19</v>
       </c>
-      <c r="G43" t="s">
-        <v>64</v>
-      </c>
-      <c r="H43">
+      <c r="G43" s="6">
+        <v>549</v>
+      </c>
+      <c r="H43" s="18">
         <v>10431</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B44" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C44" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D44" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
-      </c>
-      <c r="F44">
+        <v>42</v>
+      </c>
+      <c r="F44" s="8">
         <v>19</v>
       </c>
-      <c r="G44" t="s">
-        <v>32</v>
-      </c>
-      <c r="H44">
+      <c r="G44" s="6">
+        <v>379</v>
+      </c>
+      <c r="H44" s="18">
         <v>7201</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B45" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="C45" t="s">
         <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E45" t="s">
-        <v>54</v>
-      </c>
-      <c r="F45">
+        <v>48</v>
+      </c>
+      <c r="F45" s="8">
         <v>19</v>
       </c>
-      <c r="G45" t="s">
-        <v>64</v>
-      </c>
-      <c r="H45">
+      <c r="G45" s="6">
+        <v>549</v>
+      </c>
+      <c r="H45" s="18">
         <v>10431</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B46" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
         <v>22</v>
       </c>
       <c r="D46" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E46" t="s">
-        <v>115</v>
-      </c>
-      <c r="F46">
+        <v>103</v>
+      </c>
+      <c r="F46" s="8">
         <v>20</v>
       </c>
-      <c r="G46" t="s">
-        <v>32</v>
-      </c>
-      <c r="H46">
+      <c r="G46" s="6">
+        <v>379</v>
+      </c>
+      <c r="H46" s="18">
         <v>7580</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B47" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C47" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E47" t="s">
-        <v>63</v>
-      </c>
-      <c r="F47">
+        <v>56</v>
+      </c>
+      <c r="F47" s="8">
         <v>6</v>
       </c>
-      <c r="G47" t="s">
-        <v>64</v>
-      </c>
-      <c r="H47">
+      <c r="G47" s="6">
+        <v>549</v>
+      </c>
+      <c r="H47" s="18">
         <v>3294</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="B48" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C48" t="s">
         <v>22</v>
       </c>
       <c r="D48" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E48" t="s">
-        <v>36</v>
-      </c>
-      <c r="F48">
+        <v>33</v>
+      </c>
+      <c r="F48" s="8">
         <v>7</v>
       </c>
-      <c r="G48" t="s">
-        <v>58</v>
-      </c>
-      <c r="H48">
+      <c r="G48" s="6">
+        <v>89</v>
+      </c>
+      <c r="H48" s="18">
         <v>623</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="B49" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C49" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D49" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E49" t="s">
-        <v>50</v>
-      </c>
-      <c r="F49">
+        <v>45</v>
+      </c>
+      <c r="F49" s="8">
         <v>7</v>
       </c>
-      <c r="G49" t="s">
-        <v>143</v>
-      </c>
-      <c r="H49">
+      <c r="G49" s="6">
+        <v>269</v>
+      </c>
+      <c r="H49" s="18">
         <v>1883</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="B50" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D50" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E50" t="s">
-        <v>54</v>
-      </c>
-      <c r="F50">
+        <v>48</v>
+      </c>
+      <c r="F50" s="8">
         <v>10</v>
       </c>
-      <c r="G50" t="s">
-        <v>64</v>
-      </c>
-      <c r="H50">
+      <c r="G50" s="6">
+        <v>549</v>
+      </c>
+      <c r="H50" s="18">
         <v>5490</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B51" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C51" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D51" t="s">
         <v>23</v>
       </c>
       <c r="E51" t="s">
-        <v>46</v>
-      </c>
-      <c r="F51">
+        <v>42</v>
+      </c>
+      <c r="F51" s="8">
         <v>15</v>
       </c>
-      <c r="G51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H51">
+      <c r="G51" s="6">
+        <v>42</v>
+      </c>
+      <c r="H51" s="18">
         <v>630</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="C52" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D52" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E52" t="s">
-        <v>115</v>
-      </c>
-      <c r="F52">
+        <v>103</v>
+      </c>
+      <c r="F52" s="8">
         <v>20</v>
       </c>
-      <c r="G52" t="s">
-        <v>42</v>
-      </c>
-      <c r="H52">
+      <c r="G52" s="6">
+        <v>379</v>
+      </c>
+      <c r="H52" s="18">
         <v>7580</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="C53" t="s">
         <v>22</v>
       </c>
       <c r="D53" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E53" t="s">
-        <v>63</v>
-      </c>
-      <c r="F53">
+        <v>56</v>
+      </c>
+      <c r="F53" s="8">
         <v>7</v>
       </c>
-      <c r="G53" t="s">
-        <v>51</v>
-      </c>
-      <c r="H53">
+      <c r="G53" s="6">
+        <v>219</v>
+      </c>
+      <c r="H53" s="18">
         <v>1533</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="B54" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="C54" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D54" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E54" t="s">
-        <v>110</v>
-      </c>
-      <c r="F54">
+        <v>98</v>
+      </c>
+      <c r="F54" s="8">
         <v>16</v>
       </c>
-      <c r="G54" t="s">
-        <v>64</v>
-      </c>
-      <c r="H54">
+      <c r="G54" s="6">
+        <v>549</v>
+      </c>
+      <c r="H54" s="18">
         <v>8784</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="B55" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C55" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D55" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E55" t="s">
-        <v>84</v>
-      </c>
-      <c r="F55">
+        <v>74</v>
+      </c>
+      <c r="F55" s="8">
         <v>8</v>
       </c>
-      <c r="G55" t="s">
-        <v>155</v>
-      </c>
-      <c r="H55">
+      <c r="G55" s="6">
+        <v>89</v>
+      </c>
+      <c r="H55" s="18">
         <v>712</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B56" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="C56" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D56" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E56" t="s">
-        <v>110</v>
-      </c>
-      <c r="F56">
+        <v>98</v>
+      </c>
+      <c r="F56" s="8">
         <v>14</v>
       </c>
-      <c r="G56" t="s">
-        <v>88</v>
-      </c>
-      <c r="H56">
+      <c r="G56" s="6">
+        <v>269</v>
+      </c>
+      <c r="H56" s="18">
         <v>3766</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="B57" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="C57" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D57" t="s">
         <v>23</v>
       </c>
       <c r="E57" t="s">
-        <v>36</v>
-      </c>
-      <c r="F57">
+        <v>33</v>
+      </c>
+      <c r="F57" s="8">
         <v>7</v>
       </c>
-      <c r="G57" t="s">
-        <v>26</v>
-      </c>
-      <c r="H57">
+      <c r="G57" s="6">
+        <v>42</v>
+      </c>
+      <c r="H57" s="18">
         <v>294</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>160</v>
-      </c>
-      <c r="H58">
+        <v>146</v>
+      </c>
+      <c r="H58" s="18">
         <v>94162</v>
       </c>
     </row>

--- a/Day 1/Guerrilla AI - Day 1 - Demo Start.xlsx
+++ b/Day 1/Guerrilla AI - Day 1 - Demo Start.xlsx
@@ -969,8 +969,10 @@
       <c r="C2" s="10"/>
     </row>
     <row r="3" spans="2:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="13" t="s">
-        <v>2</v>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Watch live. Reply in chat with a word or letter when invited. Try the workbook afterward at your own pace.</t>
+        </is>
       </c>
       <c r="C3" s="10"/>
     </row>
@@ -981,8 +983,10 @@
       <c r="C5" s="10"/>
     </row>
     <row r="6" spans="2:3" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="9" t="s">
-        <v>4</v>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Email changes later. Will Flash Fill update? YES / NO. Reply in chat or think of your choice.</t>
+        </is>
       </c>
       <c r="C6" s="10"/>
     </row>
@@ -990,8 +994,15 @@
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>6</v>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Split a clean name out of the email column
+1. On raw-export, click cell I1 and type: Rep Name
+2. In I2, type the answer for row 2: Marcus Webb
+3. Press Enter, then press Ctrl+E (Flash Fill)
+4. Watch the whole column fill from your one example
+5. Spot-check two rows near the bottom</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="2:3" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -1002,8 +1013,10 @@
       <c r="C10" s="10"/>
     </row>
     <row r="11" spans="2:3" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="9" t="s">
-        <v>8</v>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Before adding up sales: keep the TOTAL rows? KEEP / REMOVE. Reply in chat or think of your choice.</t>
+        </is>
       </c>
       <c r="C11" s="10"/>
     </row>
@@ -1017,14 +1030,18 @@
     </row>
     <row r="13" spans="2:3" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="14" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="15" t="s">
-        <v>10</v>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One small next step</t>
+        </is>
       </c>
       <c r="C14" s="10"/>
     </row>
     <row r="15" spans="2:3" ht="23" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="12" t="s">
-        <v>11</v>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NAMES: try Flash Fill on one column. Or TOTALS: check one summary for subtotal rows. Pick one.</t>
+        </is>
       </c>
       <c r="C15" s="10"/>
     </row>
